--- a/data/processed/recettes_adherent.xlsx
+++ b/data/processed/recettes_adherent.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:T80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,6 +471,71 @@
           <t>date</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>trimestre</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>month_sin</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>month_cos</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lag_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>lag_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>lag_6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>moyenne_mobile</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>rolling_6</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>transactions_lag_1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>transactions_lag_3</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>transactions_rolling_3</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>transactions_diff</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>trend</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -485,7 +550,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>44927</v>
+        <v>44957</v>
       </c>
       <c r="E2" t="n">
         <v>57465</v>
@@ -494,7 +559,28 @@
         <v>204</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>44927</v>
+        <v>44957</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -510,7 +596,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>44958</v>
+        <v>44985</v>
       </c>
       <c r="E3" t="n">
         <v>69472</v>
@@ -519,7 +605,34 @@
         <v>224</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>44958</v>
+        <v>44985</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K3" t="n">
+        <v>57465</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>204</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -535,7 +648,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>44986</v>
+        <v>45016</v>
       </c>
       <c r="E4" t="n">
         <v>82135</v>
@@ -544,7 +657,34 @@
         <v>263</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>44986</v>
+        <v>45016</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="K4" t="n">
+        <v>69472</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>224</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>39</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -560,7 +700,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>45017</v>
+        <v>45046</v>
       </c>
       <c r="E5" t="n">
         <v>54472</v>
@@ -569,7 +709,42 @@
         <v>172</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>45017</v>
+        <v>45046</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="K5" t="n">
+        <v>82135</v>
+      </c>
+      <c r="L5" t="n">
+        <v>57465</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>69690.66666666667</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>263</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>204</v>
+      </c>
+      <c r="R5" t="n">
+        <v>230.3333333333333</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-91</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -585,7 +760,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>45047</v>
+        <v>45077</v>
       </c>
       <c r="E6" t="n">
         <v>71284</v>
@@ -594,7 +769,42 @@
         <v>201</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>45047</v>
+        <v>45077</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K6" t="n">
+        <v>54472</v>
+      </c>
+      <c r="L6" t="n">
+        <v>69472</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>68693</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>172</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>224</v>
+      </c>
+      <c r="R6" t="n">
+        <v>219.6666666666667</v>
+      </c>
+      <c r="S6" t="n">
+        <v>29</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -610,7 +820,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>45078</v>
+        <v>45107</v>
       </c>
       <c r="E7" t="n">
         <v>50388</v>
@@ -619,7 +829,42 @@
         <v>137</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>45078</v>
+        <v>45107</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>71284</v>
+      </c>
+      <c r="L7" t="n">
+        <v>82135</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>69297</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>201</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>263</v>
+      </c>
+      <c r="R7" t="n">
+        <v>212</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-64</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -635,7 +880,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>45108</v>
+        <v>45138</v>
       </c>
       <c r="E8" t="n">
         <v>48645</v>
@@ -644,7 +889,46 @@
         <v>120</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>45108</v>
+        <v>45138</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K8" t="n">
+        <v>50388</v>
+      </c>
+      <c r="L8" t="n">
+        <v>54472</v>
+      </c>
+      <c r="M8" t="n">
+        <v>57465</v>
+      </c>
+      <c r="N8" t="n">
+        <v>58714.66666666666</v>
+      </c>
+      <c r="O8" t="n">
+        <v>64202.66666666666</v>
+      </c>
+      <c r="P8" t="n">
+        <v>137</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>172</v>
+      </c>
+      <c r="R8" t="n">
+        <v>170</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-17</v>
+      </c>
+      <c r="T8" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -660,7 +944,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>45139</v>
+        <v>45169</v>
       </c>
       <c r="E9" t="n">
         <v>111371</v>
@@ -669,7 +953,46 @@
         <v>304</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>45139</v>
+        <v>45169</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K9" t="n">
+        <v>48645</v>
+      </c>
+      <c r="L9" t="n">
+        <v>71284</v>
+      </c>
+      <c r="M9" t="n">
+        <v>69472</v>
+      </c>
+      <c r="N9" t="n">
+        <v>56772.33333333334</v>
+      </c>
+      <c r="O9" t="n">
+        <v>62732.66666666666</v>
+      </c>
+      <c r="P9" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>201</v>
+      </c>
+      <c r="R9" t="n">
+        <v>152.6666666666667</v>
+      </c>
+      <c r="S9" t="n">
+        <v>184</v>
+      </c>
+      <c r="T9" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -685,7 +1008,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>45170</v>
+        <v>45199</v>
       </c>
       <c r="E10" t="n">
         <v>56903</v>
@@ -694,7 +1017,46 @@
         <v>155</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>45170</v>
+        <v>45199</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="K10" t="n">
+        <v>111371</v>
+      </c>
+      <c r="L10" t="n">
+        <v>50388</v>
+      </c>
+      <c r="M10" t="n">
+        <v>82135</v>
+      </c>
+      <c r="N10" t="n">
+        <v>70134.66666666667</v>
+      </c>
+      <c r="O10" t="n">
+        <v>69715.83333333333</v>
+      </c>
+      <c r="P10" t="n">
+        <v>304</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>137</v>
+      </c>
+      <c r="R10" t="n">
+        <v>187</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-149</v>
+      </c>
+      <c r="T10" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -710,7 +1072,7 @@
         <v>10</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>45200</v>
+        <v>45230</v>
       </c>
       <c r="E11" t="n">
         <v>72834</v>
@@ -719,7 +1081,46 @@
         <v>236</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>45200</v>
+        <v>45230</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K11" t="n">
+        <v>56903</v>
+      </c>
+      <c r="L11" t="n">
+        <v>48645</v>
+      </c>
+      <c r="M11" t="n">
+        <v>54472</v>
+      </c>
+      <c r="N11" t="n">
+        <v>72306.33333333333</v>
+      </c>
+      <c r="O11" t="n">
+        <v>65510.5</v>
+      </c>
+      <c r="P11" t="n">
+        <v>155</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>120</v>
+      </c>
+      <c r="R11" t="n">
+        <v>193</v>
+      </c>
+      <c r="S11" t="n">
+        <v>81</v>
+      </c>
+      <c r="T11" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -735,7 +1136,7 @@
         <v>11</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>45231</v>
+        <v>45260</v>
       </c>
       <c r="E12" t="n">
         <v>70258</v>
@@ -744,7 +1145,46 @@
         <v>226</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>45231</v>
+        <v>45260</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K12" t="n">
+        <v>72834</v>
+      </c>
+      <c r="L12" t="n">
+        <v>111371</v>
+      </c>
+      <c r="M12" t="n">
+        <v>71284</v>
+      </c>
+      <c r="N12" t="n">
+        <v>80369.33333333333</v>
+      </c>
+      <c r="O12" t="n">
+        <v>68570.83333333333</v>
+      </c>
+      <c r="P12" t="n">
+        <v>236</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>304</v>
+      </c>
+      <c r="R12" t="n">
+        <v>231.6666666666667</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-10</v>
+      </c>
+      <c r="T12" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -760,7 +1200,7 @@
         <v>12</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>45261</v>
+        <v>45291</v>
       </c>
       <c r="E13" t="n">
         <v>58997</v>
@@ -769,7 +1209,46 @@
         <v>188</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>45261</v>
+        <v>45291</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>70258</v>
+      </c>
+      <c r="L13" t="n">
+        <v>56903</v>
+      </c>
+      <c r="M13" t="n">
+        <v>50388</v>
+      </c>
+      <c r="N13" t="n">
+        <v>66665</v>
+      </c>
+      <c r="O13" t="n">
+        <v>68399.83333333333</v>
+      </c>
+      <c r="P13" t="n">
+        <v>226</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>155</v>
+      </c>
+      <c r="R13" t="n">
+        <v>205.6666666666667</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-38</v>
+      </c>
+      <c r="T13" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="14">
@@ -785,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>45292</v>
+        <v>45322</v>
       </c>
       <c r="E14" t="n">
         <v>61234</v>
@@ -794,7 +1273,46 @@
         <v>198</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>45292</v>
+        <v>45322</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K14" t="n">
+        <v>58997</v>
+      </c>
+      <c r="L14" t="n">
+        <v>72834</v>
+      </c>
+      <c r="M14" t="n">
+        <v>48645</v>
+      </c>
+      <c r="N14" t="n">
+        <v>67363</v>
+      </c>
+      <c r="O14" t="n">
+        <v>69834.66666666667</v>
+      </c>
+      <c r="P14" t="n">
+        <v>188</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>236</v>
+      </c>
+      <c r="R14" t="n">
+        <v>216.6666666666667</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -810,7 +1328,7 @@
         <v>2</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>45323</v>
+        <v>45351</v>
       </c>
       <c r="E15" t="n">
         <v>65704</v>
@@ -819,7 +1337,46 @@
         <v>210</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>45323</v>
+        <v>45351</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K15" t="n">
+        <v>61234</v>
+      </c>
+      <c r="L15" t="n">
+        <v>70258</v>
+      </c>
+      <c r="M15" t="n">
+        <v>111371</v>
+      </c>
+      <c r="N15" t="n">
+        <v>63496.33333333334</v>
+      </c>
+      <c r="O15" t="n">
+        <v>71932.83333333333</v>
+      </c>
+      <c r="P15" t="n">
+        <v>198</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>226</v>
+      </c>
+      <c r="R15" t="n">
+        <v>204</v>
+      </c>
+      <c r="S15" t="n">
+        <v>12</v>
+      </c>
+      <c r="T15" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -835,7 +1392,7 @@
         <v>3</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>45352</v>
+        <v>45382</v>
       </c>
       <c r="E16" t="n">
         <v>53894</v>
@@ -844,7 +1401,46 @@
         <v>241</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>45352</v>
+        <v>45382</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="K16" t="n">
+        <v>65704</v>
+      </c>
+      <c r="L16" t="n">
+        <v>58997</v>
+      </c>
+      <c r="M16" t="n">
+        <v>56903</v>
+      </c>
+      <c r="N16" t="n">
+        <v>61978.33333333334</v>
+      </c>
+      <c r="O16" t="n">
+        <v>64321.66666666666</v>
+      </c>
+      <c r="P16" t="n">
+        <v>210</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>188</v>
+      </c>
+      <c r="R16" t="n">
+        <v>198.6666666666667</v>
+      </c>
+      <c r="S16" t="n">
+        <v>31</v>
+      </c>
+      <c r="T16" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -860,7 +1456,7 @@
         <v>4</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>45383</v>
+        <v>45412</v>
       </c>
       <c r="E17" t="n">
         <v>100386</v>
@@ -869,7 +1465,46 @@
         <v>278</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>45383</v>
+        <v>45412</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="K17" t="n">
+        <v>53894</v>
+      </c>
+      <c r="L17" t="n">
+        <v>61234</v>
+      </c>
+      <c r="M17" t="n">
+        <v>72834</v>
+      </c>
+      <c r="N17" t="n">
+        <v>60277.33333333334</v>
+      </c>
+      <c r="O17" t="n">
+        <v>63820.16666666666</v>
+      </c>
+      <c r="P17" t="n">
+        <v>241</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>198</v>
+      </c>
+      <c r="R17" t="n">
+        <v>216.3333333333333</v>
+      </c>
+      <c r="S17" t="n">
+        <v>37</v>
+      </c>
+      <c r="T17" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -885,7 +1520,7 @@
         <v>5</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>45413</v>
+        <v>45443</v>
       </c>
       <c r="E18" t="n">
         <v>78797</v>
@@ -894,7 +1529,46 @@
         <v>216</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>45413</v>
+        <v>45443</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K18" t="n">
+        <v>100386</v>
+      </c>
+      <c r="L18" t="n">
+        <v>65704</v>
+      </c>
+      <c r="M18" t="n">
+        <v>70258</v>
+      </c>
+      <c r="N18" t="n">
+        <v>73328</v>
+      </c>
+      <c r="O18" t="n">
+        <v>68412.16666666667</v>
+      </c>
+      <c r="P18" t="n">
+        <v>278</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>210</v>
+      </c>
+      <c r="R18" t="n">
+        <v>243</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-62</v>
+      </c>
+      <c r="T18" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="19">
@@ -910,7 +1584,7 @@
         <v>6</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>45444</v>
+        <v>45473</v>
       </c>
       <c r="E19" t="n">
         <v>267687</v>
@@ -919,7 +1593,46 @@
         <v>392</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>45444</v>
+        <v>45473</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>78797</v>
+      </c>
+      <c r="L19" t="n">
+        <v>53894</v>
+      </c>
+      <c r="M19" t="n">
+        <v>58997</v>
+      </c>
+      <c r="N19" t="n">
+        <v>77692.33333333333</v>
+      </c>
+      <c r="O19" t="n">
+        <v>69835.33333333333</v>
+      </c>
+      <c r="P19" t="n">
+        <v>216</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>241</v>
+      </c>
+      <c r="R19" t="n">
+        <v>245</v>
+      </c>
+      <c r="S19" t="n">
+        <v>176</v>
+      </c>
+      <c r="T19" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="20">
@@ -935,7 +1648,7 @@
         <v>7</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>45474</v>
+        <v>45504</v>
       </c>
       <c r="E20" t="n">
         <v>82435</v>
@@ -944,7 +1657,46 @@
         <v>235</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>45474</v>
+        <v>45504</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K20" t="n">
+        <v>267687</v>
+      </c>
+      <c r="L20" t="n">
+        <v>100386</v>
+      </c>
+      <c r="M20" t="n">
+        <v>61234</v>
+      </c>
+      <c r="N20" t="n">
+        <v>148956.6666666667</v>
+      </c>
+      <c r="O20" t="n">
+        <v>104617</v>
+      </c>
+      <c r="P20" t="n">
+        <v>392</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>278</v>
+      </c>
+      <c r="R20" t="n">
+        <v>295.3333333333333</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-157</v>
+      </c>
+      <c r="T20" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -960,7 +1712,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>45505</v>
+        <v>45535</v>
       </c>
       <c r="E21" t="n">
         <v>86408</v>
@@ -969,7 +1721,46 @@
         <v>273</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>45505</v>
+        <v>45535</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K21" t="n">
+        <v>82435</v>
+      </c>
+      <c r="L21" t="n">
+        <v>78797</v>
+      </c>
+      <c r="M21" t="n">
+        <v>65704</v>
+      </c>
+      <c r="N21" t="n">
+        <v>142973</v>
+      </c>
+      <c r="O21" t="n">
+        <v>108150.5</v>
+      </c>
+      <c r="P21" t="n">
+        <v>235</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>216</v>
+      </c>
+      <c r="R21" t="n">
+        <v>281</v>
+      </c>
+      <c r="S21" t="n">
+        <v>38</v>
+      </c>
+      <c r="T21" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="22">
@@ -985,7 +1776,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>45536</v>
+        <v>45565</v>
       </c>
       <c r="E22" t="n">
         <v>67386</v>
@@ -994,7 +1785,46 @@
         <v>193</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>45536</v>
+        <v>45565</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="K22" t="n">
+        <v>86408</v>
+      </c>
+      <c r="L22" t="n">
+        <v>267687</v>
+      </c>
+      <c r="M22" t="n">
+        <v>53894</v>
+      </c>
+      <c r="N22" t="n">
+        <v>145510</v>
+      </c>
+      <c r="O22" t="n">
+        <v>111601.1666666667</v>
+      </c>
+      <c r="P22" t="n">
+        <v>273</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>392</v>
+      </c>
+      <c r="R22" t="n">
+        <v>300</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-80</v>
+      </c>
+      <c r="T22" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -1010,7 +1840,7 @@
         <v>10</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>45566</v>
+        <v>45596</v>
       </c>
       <c r="E23" t="n">
         <v>99655</v>
@@ -1019,7 +1849,46 @@
         <v>283</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>45566</v>
+        <v>45596</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K23" t="n">
+        <v>67386</v>
+      </c>
+      <c r="L23" t="n">
+        <v>82435</v>
+      </c>
+      <c r="M23" t="n">
+        <v>100386</v>
+      </c>
+      <c r="N23" t="n">
+        <v>78743</v>
+      </c>
+      <c r="O23" t="n">
+        <v>113849.8333333333</v>
+      </c>
+      <c r="P23" t="n">
+        <v>193</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>235</v>
+      </c>
+      <c r="R23" t="n">
+        <v>233.6666666666667</v>
+      </c>
+      <c r="S23" t="n">
+        <v>90</v>
+      </c>
+      <c r="T23" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="24">
@@ -1035,7 +1904,7 @@
         <v>11</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>45597</v>
+        <v>45626</v>
       </c>
       <c r="E24" t="n">
         <v>89916</v>
@@ -1044,7 +1913,46 @@
         <v>232</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>45597</v>
+        <v>45626</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K24" t="n">
+        <v>99655</v>
+      </c>
+      <c r="L24" t="n">
+        <v>86408</v>
+      </c>
+      <c r="M24" t="n">
+        <v>78797</v>
+      </c>
+      <c r="N24" t="n">
+        <v>84483</v>
+      </c>
+      <c r="O24" t="n">
+        <v>113728</v>
+      </c>
+      <c r="P24" t="n">
+        <v>283</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>273</v>
+      </c>
+      <c r="R24" t="n">
+        <v>249.6666666666667</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-51</v>
+      </c>
+      <c r="T24" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -1060,7 +1968,7 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>45627</v>
+        <v>45657</v>
       </c>
       <c r="E25" t="n">
         <v>93306</v>
@@ -1069,7 +1977,46 @@
         <v>235</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>45627</v>
+        <v>45657</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>89916</v>
+      </c>
+      <c r="L25" t="n">
+        <v>67386</v>
+      </c>
+      <c r="M25" t="n">
+        <v>267687</v>
+      </c>
+      <c r="N25" t="n">
+        <v>85652.33333333333</v>
+      </c>
+      <c r="O25" t="n">
+        <v>115581.1666666667</v>
+      </c>
+      <c r="P25" t="n">
+        <v>232</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>193</v>
+      </c>
+      <c r="R25" t="n">
+        <v>236</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="26">
@@ -1085,7 +2032,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>45658</v>
+        <v>45688</v>
       </c>
       <c r="E26" t="n">
         <v>77591</v>
@@ -1094,7 +2041,46 @@
         <v>255</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>45658</v>
+        <v>45688</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K26" t="n">
+        <v>93306</v>
+      </c>
+      <c r="L26" t="n">
+        <v>99655</v>
+      </c>
+      <c r="M26" t="n">
+        <v>82435</v>
+      </c>
+      <c r="N26" t="n">
+        <v>94292.33333333333</v>
+      </c>
+      <c r="O26" t="n">
+        <v>86517.66666666667</v>
+      </c>
+      <c r="P26" t="n">
+        <v>235</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>283</v>
+      </c>
+      <c r="R26" t="n">
+        <v>250</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="27">
@@ -1110,7 +2096,7 @@
         <v>2</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>45689</v>
+        <v>45716</v>
       </c>
       <c r="E27" t="n">
         <v>68980</v>
@@ -1119,7 +2105,46 @@
         <v>193</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>45689</v>
+        <v>45716</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K27" t="n">
+        <v>77591</v>
+      </c>
+      <c r="L27" t="n">
+        <v>89916</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86408</v>
+      </c>
+      <c r="N27" t="n">
+        <v>86937.66666666667</v>
+      </c>
+      <c r="O27" t="n">
+        <v>85710.33333333333</v>
+      </c>
+      <c r="P27" t="n">
+        <v>255</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>232</v>
+      </c>
+      <c r="R27" t="n">
+        <v>240.6666666666667</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-62</v>
+      </c>
+      <c r="T27" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="28">
@@ -1135,7 +2160,7 @@
         <v>3</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>45717</v>
+        <v>45747</v>
       </c>
       <c r="E28" t="n">
         <v>80476</v>
@@ -1144,7 +2169,46 @@
         <v>217</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>45717</v>
+        <v>45747</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="K28" t="n">
+        <v>68980</v>
+      </c>
+      <c r="L28" t="n">
+        <v>93306</v>
+      </c>
+      <c r="M28" t="n">
+        <v>67386</v>
+      </c>
+      <c r="N28" t="n">
+        <v>79959</v>
+      </c>
+      <c r="O28" t="n">
+        <v>82805.66666666667</v>
+      </c>
+      <c r="P28" t="n">
+        <v>193</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>235</v>
+      </c>
+      <c r="R28" t="n">
+        <v>227.6666666666667</v>
+      </c>
+      <c r="S28" t="n">
+        <v>24</v>
+      </c>
+      <c r="T28" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="29">
@@ -1160,7 +2224,7 @@
         <v>4</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>45748</v>
+        <v>45777</v>
       </c>
       <c r="E29" t="n">
         <v>82015</v>
@@ -1169,7 +2233,46 @@
         <v>248</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>45748</v>
+        <v>45777</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="K29" t="n">
+        <v>80476</v>
+      </c>
+      <c r="L29" t="n">
+        <v>77591</v>
+      </c>
+      <c r="M29" t="n">
+        <v>99655</v>
+      </c>
+      <c r="N29" t="n">
+        <v>75682.33333333333</v>
+      </c>
+      <c r="O29" t="n">
+        <v>84987.33333333333</v>
+      </c>
+      <c r="P29" t="n">
+        <v>217</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>255</v>
+      </c>
+      <c r="R29" t="n">
+        <v>221.6666666666667</v>
+      </c>
+      <c r="S29" t="n">
+        <v>31</v>
+      </c>
+      <c r="T29" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="30">
@@ -1185,7 +2288,7 @@
         <v>5</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>45778</v>
+        <v>45808</v>
       </c>
       <c r="E30" t="n">
         <v>78820</v>
@@ -1194,7 +2297,46 @@
         <v>213</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>45778</v>
+        <v>45808</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K30" t="n">
+        <v>82015</v>
+      </c>
+      <c r="L30" t="n">
+        <v>68980</v>
+      </c>
+      <c r="M30" t="n">
+        <v>89916</v>
+      </c>
+      <c r="N30" t="n">
+        <v>77157</v>
+      </c>
+      <c r="O30" t="n">
+        <v>82047.33333333333</v>
+      </c>
+      <c r="P30" t="n">
+        <v>248</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>193</v>
+      </c>
+      <c r="R30" t="n">
+        <v>219.3333333333333</v>
+      </c>
+      <c r="S30" t="n">
+        <v>-35</v>
+      </c>
+      <c r="T30" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="31">
@@ -1210,7 +2352,7 @@
         <v>6</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>45809</v>
+        <v>45838</v>
       </c>
       <c r="E31" t="n">
         <v>61067</v>
@@ -1219,7 +2361,46 @@
         <v>158</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>45809</v>
+        <v>45838</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>78820</v>
+      </c>
+      <c r="L31" t="n">
+        <v>80476</v>
+      </c>
+      <c r="M31" t="n">
+        <v>93306</v>
+      </c>
+      <c r="N31" t="n">
+        <v>80437</v>
+      </c>
+      <c r="O31" t="n">
+        <v>80198</v>
+      </c>
+      <c r="P31" t="n">
+        <v>213</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>217</v>
+      </c>
+      <c r="R31" t="n">
+        <v>226</v>
+      </c>
+      <c r="S31" t="n">
+        <v>-55</v>
+      </c>
+      <c r="T31" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="32">
@@ -1235,7 +2416,7 @@
         <v>7</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>45839</v>
+        <v>45869</v>
       </c>
       <c r="E32" t="n">
         <v>66771</v>
@@ -1244,7 +2425,46 @@
         <v>172</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>45839</v>
+        <v>45869</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K32" t="n">
+        <v>61067</v>
+      </c>
+      <c r="L32" t="n">
+        <v>82015</v>
+      </c>
+      <c r="M32" t="n">
+        <v>77591</v>
+      </c>
+      <c r="N32" t="n">
+        <v>73967.33333333333</v>
+      </c>
+      <c r="O32" t="n">
+        <v>74824.83333333333</v>
+      </c>
+      <c r="P32" t="n">
+        <v>158</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>248</v>
+      </c>
+      <c r="R32" t="n">
+        <v>206.3333333333333</v>
+      </c>
+      <c r="S32" t="n">
+        <v>14</v>
+      </c>
+      <c r="T32" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="33">
@@ -1260,7 +2480,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>45870</v>
+        <v>45900</v>
       </c>
       <c r="E33" t="n">
         <v>52650</v>
@@ -1269,7 +2489,46 @@
         <v>131</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>45870</v>
+        <v>45900</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K33" t="n">
+        <v>66771</v>
+      </c>
+      <c r="L33" t="n">
+        <v>78820</v>
+      </c>
+      <c r="M33" t="n">
+        <v>68980</v>
+      </c>
+      <c r="N33" t="n">
+        <v>68886</v>
+      </c>
+      <c r="O33" t="n">
+        <v>73021.5</v>
+      </c>
+      <c r="P33" t="n">
+        <v>172</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>213</v>
+      </c>
+      <c r="R33" t="n">
+        <v>181</v>
+      </c>
+      <c r="S33" t="n">
+        <v>-41</v>
+      </c>
+      <c r="T33" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="34">
@@ -1285,7 +2544,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>45901</v>
+        <v>45930</v>
       </c>
       <c r="E34" t="n">
         <v>65680</v>
@@ -1294,7 +2553,46 @@
         <v>209</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>45901</v>
+        <v>45930</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="K34" t="n">
+        <v>52650</v>
+      </c>
+      <c r="L34" t="n">
+        <v>61067</v>
+      </c>
+      <c r="M34" t="n">
+        <v>80476</v>
+      </c>
+      <c r="N34" t="n">
+        <v>60162.66666666666</v>
+      </c>
+      <c r="O34" t="n">
+        <v>70299.83333333333</v>
+      </c>
+      <c r="P34" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>158</v>
+      </c>
+      <c r="R34" t="n">
+        <v>153.6666666666667</v>
+      </c>
+      <c r="S34" t="n">
+        <v>78</v>
+      </c>
+      <c r="T34" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="35">
@@ -1310,7 +2608,7 @@
         <v>10</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>45931</v>
+        <v>45961</v>
       </c>
       <c r="E35" t="n">
         <v>91471</v>
@@ -1319,7 +2617,46 @@
         <v>228</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>45931</v>
+        <v>45961</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K35" t="n">
+        <v>65680</v>
+      </c>
+      <c r="L35" t="n">
+        <v>66771</v>
+      </c>
+      <c r="M35" t="n">
+        <v>82015</v>
+      </c>
+      <c r="N35" t="n">
+        <v>61700.33333333334</v>
+      </c>
+      <c r="O35" t="n">
+        <v>67833.83333333333</v>
+      </c>
+      <c r="P35" t="n">
+        <v>209</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>172</v>
+      </c>
+      <c r="R35" t="n">
+        <v>170.6666666666667</v>
+      </c>
+      <c r="S35" t="n">
+        <v>19</v>
+      </c>
+      <c r="T35" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="36">
@@ -1335,7 +2672,7 @@
         <v>11</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>45962</v>
+        <v>45991</v>
       </c>
       <c r="E36" t="n">
         <v>60911</v>
@@ -1344,7 +2681,46 @@
         <v>174</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>45962</v>
+        <v>45991</v>
+      </c>
+      <c r="H36" t="n">
+        <v>4</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K36" t="n">
+        <v>91471</v>
+      </c>
+      <c r="L36" t="n">
+        <v>52650</v>
+      </c>
+      <c r="M36" t="n">
+        <v>78820</v>
+      </c>
+      <c r="N36" t="n">
+        <v>69933.66666666667</v>
+      </c>
+      <c r="O36" t="n">
+        <v>69409.83333333333</v>
+      </c>
+      <c r="P36" t="n">
+        <v>228</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>131</v>
+      </c>
+      <c r="R36" t="n">
+        <v>189.3333333333333</v>
+      </c>
+      <c r="S36" t="n">
+        <v>-54</v>
+      </c>
+      <c r="T36" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="37">
@@ -1360,7 +2736,7 @@
         <v>12</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>45992</v>
+        <v>46022</v>
       </c>
       <c r="E37" t="n">
         <v>74438</v>
@@ -1369,7 +2745,46 @@
         <v>189</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>45992</v>
+        <v>46022</v>
+      </c>
+      <c r="H37" t="n">
+        <v>4</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>60911</v>
+      </c>
+      <c r="L37" t="n">
+        <v>65680</v>
+      </c>
+      <c r="M37" t="n">
+        <v>61067</v>
+      </c>
+      <c r="N37" t="n">
+        <v>72687.33333333333</v>
+      </c>
+      <c r="O37" t="n">
+        <v>66425</v>
+      </c>
+      <c r="P37" t="n">
+        <v>174</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>209</v>
+      </c>
+      <c r="R37" t="n">
+        <v>203.6666666666667</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="38">
@@ -1385,7 +2800,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>44927</v>
+        <v>44957</v>
       </c>
       <c r="E38" t="n">
         <v>43250</v>
@@ -1394,7 +2809,28 @@
         <v>588</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>44927</v>
+        <v>44957</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1410,7 +2846,7 @@
         <v>2</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>44958</v>
+        <v>44985</v>
       </c>
       <c r="E39" t="n">
         <v>35850</v>
@@ -1419,7 +2855,34 @@
         <v>489</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>44958</v>
+        <v>44985</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K39" t="n">
+        <v>43250</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="n">
+        <v>588</v>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="n">
+        <v>-99</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1435,7 +2898,7 @@
         <v>3</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>44986</v>
+        <v>45016</v>
       </c>
       <c r="E40" t="n">
         <v>32850</v>
@@ -1444,7 +2907,34 @@
         <v>452</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>44986</v>
+        <v>45016</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="K40" t="n">
+        <v>35850</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="n">
+        <v>489</v>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="n">
+        <v>-37</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -1460,7 +2950,7 @@
         <v>4</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>45017</v>
+        <v>45046</v>
       </c>
       <c r="E41" t="n">
         <v>30000</v>
@@ -1469,7 +2959,42 @@
         <v>416</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>45017</v>
+        <v>45046</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J41" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="K41" t="n">
+        <v>32850</v>
+      </c>
+      <c r="L41" t="n">
+        <v>43250</v>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="n">
+        <v>37316.66666666666</v>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="n">
+        <v>452</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>588</v>
+      </c>
+      <c r="R41" t="n">
+        <v>509.6666666666667</v>
+      </c>
+      <c r="S41" t="n">
+        <v>-36</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -1485,7 +3010,7 @@
         <v>5</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>45047</v>
+        <v>45077</v>
       </c>
       <c r="E42" t="n">
         <v>37000</v>
@@ -1494,7 +3019,42 @@
         <v>515</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>45047</v>
+        <v>45077</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K42" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L42" t="n">
+        <v>35850</v>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>32900</v>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="n">
+        <v>416</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>489</v>
+      </c>
+      <c r="R42" t="n">
+        <v>452.3333333333333</v>
+      </c>
+      <c r="S42" t="n">
+        <v>99</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -1510,7 +3070,7 @@
         <v>6</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>45078</v>
+        <v>45107</v>
       </c>
       <c r="E43" t="n">
         <v>29400</v>
@@ -1519,7 +3079,42 @@
         <v>367</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>45078</v>
+        <v>45107</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K43" t="n">
+        <v>37000</v>
+      </c>
+      <c r="L43" t="n">
+        <v>32850</v>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="n">
+        <v>33283.33333333334</v>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="n">
+        <v>515</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>452</v>
+      </c>
+      <c r="R43" t="n">
+        <v>461</v>
+      </c>
+      <c r="S43" t="n">
+        <v>-148</v>
+      </c>
+      <c r="T43" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="44">
@@ -1535,7 +3130,7 @@
         <v>7</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>45108</v>
+        <v>45138</v>
       </c>
       <c r="E44" t="n">
         <v>15700</v>
@@ -1544,7 +3139,46 @@
         <v>225</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>45108</v>
+        <v>45138</v>
+      </c>
+      <c r="H44" t="n">
+        <v>3</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J44" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K44" t="n">
+        <v>29400</v>
+      </c>
+      <c r="L44" t="n">
+        <v>30000</v>
+      </c>
+      <c r="M44" t="n">
+        <v>43250</v>
+      </c>
+      <c r="N44" t="n">
+        <v>32133.33333333333</v>
+      </c>
+      <c r="O44" t="n">
+        <v>34725</v>
+      </c>
+      <c r="P44" t="n">
+        <v>367</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>416</v>
+      </c>
+      <c r="R44" t="n">
+        <v>432.6666666666667</v>
+      </c>
+      <c r="S44" t="n">
+        <v>-142</v>
+      </c>
+      <c r="T44" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="45">
@@ -1560,7 +3194,7 @@
         <v>8</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>45139</v>
+        <v>45169</v>
       </c>
       <c r="E45" t="n">
         <v>25300</v>
@@ -1569,7 +3203,46 @@
         <v>356</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>45139</v>
+        <v>45169</v>
+      </c>
+      <c r="H45" t="n">
+        <v>3</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J45" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K45" t="n">
+        <v>15700</v>
+      </c>
+      <c r="L45" t="n">
+        <v>37000</v>
+      </c>
+      <c r="M45" t="n">
+        <v>35850</v>
+      </c>
+      <c r="N45" t="n">
+        <v>27366.66666666667</v>
+      </c>
+      <c r="O45" t="n">
+        <v>30133.33333333333</v>
+      </c>
+      <c r="P45" t="n">
+        <v>225</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>515</v>
+      </c>
+      <c r="R45" t="n">
+        <v>369</v>
+      </c>
+      <c r="S45" t="n">
+        <v>131</v>
+      </c>
+      <c r="T45" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="46">
@@ -1585,7 +3258,7 @@
         <v>9</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>45170</v>
+        <v>45199</v>
       </c>
       <c r="E46" t="n">
         <v>33100</v>
@@ -1594,7 +3267,46 @@
         <v>455</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>45170</v>
+        <v>45199</v>
+      </c>
+      <c r="H46" t="n">
+        <v>3</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="K46" t="n">
+        <v>25300</v>
+      </c>
+      <c r="L46" t="n">
+        <v>29400</v>
+      </c>
+      <c r="M46" t="n">
+        <v>32850</v>
+      </c>
+      <c r="N46" t="n">
+        <v>23466.66666666667</v>
+      </c>
+      <c r="O46" t="n">
+        <v>28375</v>
+      </c>
+      <c r="P46" t="n">
+        <v>356</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>367</v>
+      </c>
+      <c r="R46" t="n">
+        <v>316</v>
+      </c>
+      <c r="S46" t="n">
+        <v>99</v>
+      </c>
+      <c r="T46" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="47">
@@ -1610,7 +3322,7 @@
         <v>10</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>45200</v>
+        <v>45230</v>
       </c>
       <c r="E47" t="n">
         <v>41350</v>
@@ -1619,7 +3331,46 @@
         <v>575</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>45200</v>
+        <v>45230</v>
+      </c>
+      <c r="H47" t="n">
+        <v>4</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K47" t="n">
+        <v>33100</v>
+      </c>
+      <c r="L47" t="n">
+        <v>15700</v>
+      </c>
+      <c r="M47" t="n">
+        <v>30000</v>
+      </c>
+      <c r="N47" t="n">
+        <v>24700</v>
+      </c>
+      <c r="O47" t="n">
+        <v>28416.66666666667</v>
+      </c>
+      <c r="P47" t="n">
+        <v>455</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>225</v>
+      </c>
+      <c r="R47" t="n">
+        <v>345.3333333333333</v>
+      </c>
+      <c r="S47" t="n">
+        <v>120</v>
+      </c>
+      <c r="T47" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="48">
@@ -1635,7 +3386,7 @@
         <v>11</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>45231</v>
+        <v>45260</v>
       </c>
       <c r="E48" t="n">
         <v>41550</v>
@@ -1644,7 +3395,46 @@
         <v>572</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>45231</v>
+        <v>45260</v>
+      </c>
+      <c r="H48" t="n">
+        <v>4</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K48" t="n">
+        <v>41350</v>
+      </c>
+      <c r="L48" t="n">
+        <v>25300</v>
+      </c>
+      <c r="M48" t="n">
+        <v>37000</v>
+      </c>
+      <c r="N48" t="n">
+        <v>33250</v>
+      </c>
+      <c r="O48" t="n">
+        <v>30308.33333333333</v>
+      </c>
+      <c r="P48" t="n">
+        <v>575</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>356</v>
+      </c>
+      <c r="R48" t="n">
+        <v>462</v>
+      </c>
+      <c r="S48" t="n">
+        <v>-3</v>
+      </c>
+      <c r="T48" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="49">
@@ -1660,7 +3450,7 @@
         <v>12</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>45261</v>
+        <v>45291</v>
       </c>
       <c r="E49" t="n">
         <v>33350</v>
@@ -1669,7 +3459,46 @@
         <v>460</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>45261</v>
+        <v>45291</v>
+      </c>
+      <c r="H49" t="n">
+        <v>4</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>41550</v>
+      </c>
+      <c r="L49" t="n">
+        <v>33100</v>
+      </c>
+      <c r="M49" t="n">
+        <v>29400</v>
+      </c>
+      <c r="N49" t="n">
+        <v>38666.66666666666</v>
+      </c>
+      <c r="O49" t="n">
+        <v>31066.66666666667</v>
+      </c>
+      <c r="P49" t="n">
+        <v>572</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>455</v>
+      </c>
+      <c r="R49" t="n">
+        <v>534</v>
+      </c>
+      <c r="S49" t="n">
+        <v>-112</v>
+      </c>
+      <c r="T49" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="50">
@@ -1685,7 +3514,7 @@
         <v>1</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>45292</v>
+        <v>45322</v>
       </c>
       <c r="E50" t="n">
         <v>41300</v>
@@ -1694,7 +3523,46 @@
         <v>572</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>45292</v>
+        <v>45322</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K50" t="n">
+        <v>33350</v>
+      </c>
+      <c r="L50" t="n">
+        <v>41350</v>
+      </c>
+      <c r="M50" t="n">
+        <v>15700</v>
+      </c>
+      <c r="N50" t="n">
+        <v>38750</v>
+      </c>
+      <c r="O50" t="n">
+        <v>31725</v>
+      </c>
+      <c r="P50" t="n">
+        <v>460</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>575</v>
+      </c>
+      <c r="R50" t="n">
+        <v>535.6666666666666</v>
+      </c>
+      <c r="S50" t="n">
+        <v>112</v>
+      </c>
+      <c r="T50" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="51">
@@ -1710,7 +3578,7 @@
         <v>2</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>45323</v>
+        <v>45351</v>
       </c>
       <c r="E51" t="n">
         <v>40550</v>
@@ -1719,7 +3587,46 @@
         <v>560</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>45323</v>
+        <v>45351</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K51" t="n">
+        <v>41300</v>
+      </c>
+      <c r="L51" t="n">
+        <v>41550</v>
+      </c>
+      <c r="M51" t="n">
+        <v>25300</v>
+      </c>
+      <c r="N51" t="n">
+        <v>38733.33333333334</v>
+      </c>
+      <c r="O51" t="n">
+        <v>35991.66666666666</v>
+      </c>
+      <c r="P51" t="n">
+        <v>572</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>572</v>
+      </c>
+      <c r="R51" t="n">
+        <v>534.6666666666666</v>
+      </c>
+      <c r="S51" t="n">
+        <v>-12</v>
+      </c>
+      <c r="T51" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="52">
@@ -1735,7 +3642,7 @@
         <v>3</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>45352</v>
+        <v>45382</v>
       </c>
       <c r="E52" t="n">
         <v>26650</v>
@@ -1744,7 +3651,46 @@
         <v>370</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>45352</v>
+        <v>45382</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="K52" t="n">
+        <v>40550</v>
+      </c>
+      <c r="L52" t="n">
+        <v>33350</v>
+      </c>
+      <c r="M52" t="n">
+        <v>33100</v>
+      </c>
+      <c r="N52" t="n">
+        <v>38400</v>
+      </c>
+      <c r="O52" t="n">
+        <v>38533.33333333334</v>
+      </c>
+      <c r="P52" t="n">
+        <v>560</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>460</v>
+      </c>
+      <c r="R52" t="n">
+        <v>530.6666666666666</v>
+      </c>
+      <c r="S52" t="n">
+        <v>-190</v>
+      </c>
+      <c r="T52" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="53">
@@ -1760,7 +3706,7 @@
         <v>4</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>45383</v>
+        <v>45412</v>
       </c>
       <c r="E53" t="n">
         <v>29450</v>
@@ -1769,7 +3715,46 @@
         <v>409</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>45383</v>
+        <v>45412</v>
+      </c>
+      <c r="H53" t="n">
+        <v>2</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J53" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="K53" t="n">
+        <v>26650</v>
+      </c>
+      <c r="L53" t="n">
+        <v>41300</v>
+      </c>
+      <c r="M53" t="n">
+        <v>41350</v>
+      </c>
+      <c r="N53" t="n">
+        <v>36166.66666666666</v>
+      </c>
+      <c r="O53" t="n">
+        <v>37458.33333333334</v>
+      </c>
+      <c r="P53" t="n">
+        <v>370</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>572</v>
+      </c>
+      <c r="R53" t="n">
+        <v>500.6666666666667</v>
+      </c>
+      <c r="S53" t="n">
+        <v>39</v>
+      </c>
+      <c r="T53" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="54">
@@ -1785,7 +3770,7 @@
         <v>5</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>45413</v>
+        <v>45443</v>
       </c>
       <c r="E54" t="n">
         <v>34950</v>
@@ -1794,7 +3779,46 @@
         <v>490</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>45413</v>
+        <v>45443</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J54" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K54" t="n">
+        <v>29450</v>
+      </c>
+      <c r="L54" t="n">
+        <v>40550</v>
+      </c>
+      <c r="M54" t="n">
+        <v>41550</v>
+      </c>
+      <c r="N54" t="n">
+        <v>32216.66666666667</v>
+      </c>
+      <c r="O54" t="n">
+        <v>35475</v>
+      </c>
+      <c r="P54" t="n">
+        <v>409</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>560</v>
+      </c>
+      <c r="R54" t="n">
+        <v>446.3333333333333</v>
+      </c>
+      <c r="S54" t="n">
+        <v>81</v>
+      </c>
+      <c r="T54" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="55">
@@ -1810,7 +3834,7 @@
         <v>6</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>45444</v>
+        <v>45473</v>
       </c>
       <c r="E55" t="n">
         <v>18150</v>
@@ -1819,7 +3843,46 @@
         <v>253</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>45444</v>
+        <v>45473</v>
+      </c>
+      <c r="H55" t="n">
+        <v>2</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J55" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K55" t="n">
+        <v>34950</v>
+      </c>
+      <c r="L55" t="n">
+        <v>26650</v>
+      </c>
+      <c r="M55" t="n">
+        <v>33350</v>
+      </c>
+      <c r="N55" t="n">
+        <v>30350</v>
+      </c>
+      <c r="O55" t="n">
+        <v>34375</v>
+      </c>
+      <c r="P55" t="n">
+        <v>490</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>370</v>
+      </c>
+      <c r="R55" t="n">
+        <v>423</v>
+      </c>
+      <c r="S55" t="n">
+        <v>-237</v>
+      </c>
+      <c r="T55" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="56">
@@ -1835,7 +3898,7 @@
         <v>7</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>45474</v>
+        <v>45504</v>
       </c>
       <c r="E56" t="n">
         <v>27400</v>
@@ -1844,7 +3907,46 @@
         <v>376</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>45474</v>
+        <v>45504</v>
+      </c>
+      <c r="H56" t="n">
+        <v>3</v>
+      </c>
+      <c r="I56" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J56" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K56" t="n">
+        <v>18150</v>
+      </c>
+      <c r="L56" t="n">
+        <v>29450</v>
+      </c>
+      <c r="M56" t="n">
+        <v>41300</v>
+      </c>
+      <c r="N56" t="n">
+        <v>27516.66666666667</v>
+      </c>
+      <c r="O56" t="n">
+        <v>31841.66666666667</v>
+      </c>
+      <c r="P56" t="n">
+        <v>253</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>409</v>
+      </c>
+      <c r="R56" t="n">
+        <v>384</v>
+      </c>
+      <c r="S56" t="n">
+        <v>123</v>
+      </c>
+      <c r="T56" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="57">
@@ -1860,7 +3962,7 @@
         <v>8</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>45505</v>
+        <v>45535</v>
       </c>
       <c r="E57" t="n">
         <v>25650</v>
@@ -1869,7 +3971,46 @@
         <v>354</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>45505</v>
+        <v>45535</v>
+      </c>
+      <c r="H57" t="n">
+        <v>3</v>
+      </c>
+      <c r="I57" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J57" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K57" t="n">
+        <v>27400</v>
+      </c>
+      <c r="L57" t="n">
+        <v>34950</v>
+      </c>
+      <c r="M57" t="n">
+        <v>40550</v>
+      </c>
+      <c r="N57" t="n">
+        <v>26833.33333333333</v>
+      </c>
+      <c r="O57" t="n">
+        <v>29525</v>
+      </c>
+      <c r="P57" t="n">
+        <v>376</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>490</v>
+      </c>
+      <c r="R57" t="n">
+        <v>373</v>
+      </c>
+      <c r="S57" t="n">
+        <v>-22</v>
+      </c>
+      <c r="T57" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="58">
@@ -1885,7 +4026,7 @@
         <v>9</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>45536</v>
+        <v>45565</v>
       </c>
       <c r="E58" t="n">
         <v>32250</v>
@@ -1894,7 +4035,46 @@
         <v>447</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>45536</v>
+        <v>45565</v>
+      </c>
+      <c r="H58" t="n">
+        <v>3</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="K58" t="n">
+        <v>25650</v>
+      </c>
+      <c r="L58" t="n">
+        <v>18150</v>
+      </c>
+      <c r="M58" t="n">
+        <v>26650</v>
+      </c>
+      <c r="N58" t="n">
+        <v>23733.33333333333</v>
+      </c>
+      <c r="O58" t="n">
+        <v>27041.66666666667</v>
+      </c>
+      <c r="P58" t="n">
+        <v>354</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>253</v>
+      </c>
+      <c r="R58" t="n">
+        <v>327.6666666666667</v>
+      </c>
+      <c r="S58" t="n">
+        <v>93</v>
+      </c>
+      <c r="T58" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="59">
@@ -1910,7 +4090,7 @@
         <v>10</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>45566</v>
+        <v>45596</v>
       </c>
       <c r="E59" t="n">
         <v>42200</v>
@@ -1919,7 +4099,46 @@
         <v>577</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>45566</v>
+        <v>45596</v>
+      </c>
+      <c r="H59" t="n">
+        <v>4</v>
+      </c>
+      <c r="I59" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K59" t="n">
+        <v>32250</v>
+      </c>
+      <c r="L59" t="n">
+        <v>27400</v>
+      </c>
+      <c r="M59" t="n">
+        <v>29450</v>
+      </c>
+      <c r="N59" t="n">
+        <v>28433.33333333333</v>
+      </c>
+      <c r="O59" t="n">
+        <v>27975</v>
+      </c>
+      <c r="P59" t="n">
+        <v>447</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>376</v>
+      </c>
+      <c r="R59" t="n">
+        <v>392.3333333333333</v>
+      </c>
+      <c r="S59" t="n">
+        <v>130</v>
+      </c>
+      <c r="T59" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="60">
@@ -1935,7 +4154,7 @@
         <v>11</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>45597</v>
+        <v>45626</v>
       </c>
       <c r="E60" t="n">
         <v>34300</v>
@@ -1944,7 +4163,46 @@
         <v>473</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>45597</v>
+        <v>45626</v>
+      </c>
+      <c r="H60" t="n">
+        <v>4</v>
+      </c>
+      <c r="I60" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K60" t="n">
+        <v>42200</v>
+      </c>
+      <c r="L60" t="n">
+        <v>25650</v>
+      </c>
+      <c r="M60" t="n">
+        <v>34950</v>
+      </c>
+      <c r="N60" t="n">
+        <v>33366.66666666666</v>
+      </c>
+      <c r="O60" t="n">
+        <v>30100</v>
+      </c>
+      <c r="P60" t="n">
+        <v>577</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>354</v>
+      </c>
+      <c r="R60" t="n">
+        <v>459.3333333333333</v>
+      </c>
+      <c r="S60" t="n">
+        <v>-104</v>
+      </c>
+      <c r="T60" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="61">
@@ -1960,7 +4218,7 @@
         <v>12</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>45627</v>
+        <v>45657</v>
       </c>
       <c r="E61" t="n">
         <v>35000</v>
@@ -1969,7 +4227,46 @@
         <v>483</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>45627</v>
+        <v>45657</v>
+      </c>
+      <c r="H61" t="n">
+        <v>4</v>
+      </c>
+      <c r="I61" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>34300</v>
+      </c>
+      <c r="L61" t="n">
+        <v>32250</v>
+      </c>
+      <c r="M61" t="n">
+        <v>18150</v>
+      </c>
+      <c r="N61" t="n">
+        <v>36250</v>
+      </c>
+      <c r="O61" t="n">
+        <v>29991.66666666667</v>
+      </c>
+      <c r="P61" t="n">
+        <v>473</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>447</v>
+      </c>
+      <c r="R61" t="n">
+        <v>499</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="62">
@@ -1985,7 +4282,7 @@
         <v>1</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>45658</v>
+        <v>45688</v>
       </c>
       <c r="E62" t="n">
         <v>42150</v>
@@ -1994,7 +4291,46 @@
         <v>575</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>45658</v>
+        <v>45688</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K62" t="n">
+        <v>35000</v>
+      </c>
+      <c r="L62" t="n">
+        <v>42200</v>
+      </c>
+      <c r="M62" t="n">
+        <v>27400</v>
+      </c>
+      <c r="N62" t="n">
+        <v>37166.66666666666</v>
+      </c>
+      <c r="O62" t="n">
+        <v>32800</v>
+      </c>
+      <c r="P62" t="n">
+        <v>483</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>577</v>
+      </c>
+      <c r="R62" t="n">
+        <v>511</v>
+      </c>
+      <c r="S62" t="n">
+        <v>92</v>
+      </c>
+      <c r="T62" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="63">
@@ -2010,7 +4346,7 @@
         <v>2</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>45689</v>
+        <v>45716</v>
       </c>
       <c r="E63" t="n">
         <v>35500</v>
@@ -2019,7 +4355,46 @@
         <v>489</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>45689</v>
+        <v>45716</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K63" t="n">
+        <v>42150</v>
+      </c>
+      <c r="L63" t="n">
+        <v>34300</v>
+      </c>
+      <c r="M63" t="n">
+        <v>25650</v>
+      </c>
+      <c r="N63" t="n">
+        <v>37150</v>
+      </c>
+      <c r="O63" t="n">
+        <v>35258.33333333334</v>
+      </c>
+      <c r="P63" t="n">
+        <v>575</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>473</v>
+      </c>
+      <c r="R63" t="n">
+        <v>510.3333333333333</v>
+      </c>
+      <c r="S63" t="n">
+        <v>-86</v>
+      </c>
+      <c r="T63" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="64">
@@ -2035,7 +4410,7 @@
         <v>3</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>45717</v>
+        <v>45747</v>
       </c>
       <c r="E64" t="n">
         <v>28250</v>
@@ -2044,7 +4419,46 @@
         <v>393</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>45717</v>
+        <v>45747</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="K64" t="n">
+        <v>35500</v>
+      </c>
+      <c r="L64" t="n">
+        <v>35000</v>
+      </c>
+      <c r="M64" t="n">
+        <v>32250</v>
+      </c>
+      <c r="N64" t="n">
+        <v>37550</v>
+      </c>
+      <c r="O64" t="n">
+        <v>36900</v>
+      </c>
+      <c r="P64" t="n">
+        <v>489</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>483</v>
+      </c>
+      <c r="R64" t="n">
+        <v>515.6666666666666</v>
+      </c>
+      <c r="S64" t="n">
+        <v>-96</v>
+      </c>
+      <c r="T64" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="65">
@@ -2060,7 +4474,7 @@
         <v>4</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>45748</v>
+        <v>45777</v>
       </c>
       <c r="E65" t="n">
         <v>35850</v>
@@ -2069,7 +4483,46 @@
         <v>499</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>45748</v>
+        <v>45777</v>
+      </c>
+      <c r="H65" t="n">
+        <v>2</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J65" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="K65" t="n">
+        <v>28250</v>
+      </c>
+      <c r="L65" t="n">
+        <v>42150</v>
+      </c>
+      <c r="M65" t="n">
+        <v>42200</v>
+      </c>
+      <c r="N65" t="n">
+        <v>35300</v>
+      </c>
+      <c r="O65" t="n">
+        <v>36233.33333333334</v>
+      </c>
+      <c r="P65" t="n">
+        <v>393</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>575</v>
+      </c>
+      <c r="R65" t="n">
+        <v>485.6666666666667</v>
+      </c>
+      <c r="S65" t="n">
+        <v>106</v>
+      </c>
+      <c r="T65" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="66">
@@ -2085,7 +4538,7 @@
         <v>5</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>45778</v>
+        <v>45808</v>
       </c>
       <c r="E66" t="n">
         <v>29600</v>
@@ -2094,7 +4547,46 @@
         <v>410</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>45778</v>
+        <v>45808</v>
+      </c>
+      <c r="H66" t="n">
+        <v>2</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J66" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K66" t="n">
+        <v>35850</v>
+      </c>
+      <c r="L66" t="n">
+        <v>35500</v>
+      </c>
+      <c r="M66" t="n">
+        <v>34300</v>
+      </c>
+      <c r="N66" t="n">
+        <v>33200</v>
+      </c>
+      <c r="O66" t="n">
+        <v>35175</v>
+      </c>
+      <c r="P66" t="n">
+        <v>499</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>489</v>
+      </c>
+      <c r="R66" t="n">
+        <v>460.3333333333333</v>
+      </c>
+      <c r="S66" t="n">
+        <v>-89</v>
+      </c>
+      <c r="T66" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="67">
@@ -2110,7 +4602,7 @@
         <v>6</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>45809</v>
+        <v>45838</v>
       </c>
       <c r="E67" t="n">
         <v>22000</v>
@@ -2119,7 +4611,46 @@
         <v>312</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>45809</v>
+        <v>45838</v>
+      </c>
+      <c r="H67" t="n">
+        <v>2</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K67" t="n">
+        <v>29600</v>
+      </c>
+      <c r="L67" t="n">
+        <v>28250</v>
+      </c>
+      <c r="M67" t="n">
+        <v>35000</v>
+      </c>
+      <c r="N67" t="n">
+        <v>31233.33333333333</v>
+      </c>
+      <c r="O67" t="n">
+        <v>34391.66666666666</v>
+      </c>
+      <c r="P67" t="n">
+        <v>410</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>393</v>
+      </c>
+      <c r="R67" t="n">
+        <v>434</v>
+      </c>
+      <c r="S67" t="n">
+        <v>-98</v>
+      </c>
+      <c r="T67" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="68">
@@ -2135,7 +4666,7 @@
         <v>7</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>45839</v>
+        <v>45869</v>
       </c>
       <c r="E68" t="n">
         <v>24400</v>
@@ -2144,7 +4675,46 @@
         <v>341</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>45839</v>
+        <v>45869</v>
+      </c>
+      <c r="H68" t="n">
+        <v>3</v>
+      </c>
+      <c r="I68" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J68" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K68" t="n">
+        <v>22000</v>
+      </c>
+      <c r="L68" t="n">
+        <v>35850</v>
+      </c>
+      <c r="M68" t="n">
+        <v>42150</v>
+      </c>
+      <c r="N68" t="n">
+        <v>29150</v>
+      </c>
+      <c r="O68" t="n">
+        <v>32225</v>
+      </c>
+      <c r="P68" t="n">
+        <v>312</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>499</v>
+      </c>
+      <c r="R68" t="n">
+        <v>407</v>
+      </c>
+      <c r="S68" t="n">
+        <v>29</v>
+      </c>
+      <c r="T68" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="69">
@@ -2160,7 +4730,7 @@
         <v>8</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>45870</v>
+        <v>45900</v>
       </c>
       <c r="E69" t="n">
         <v>24050</v>
@@ -2169,7 +4739,46 @@
         <v>340</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>45870</v>
+        <v>45900</v>
+      </c>
+      <c r="H69" t="n">
+        <v>3</v>
+      </c>
+      <c r="I69" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J69" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K69" t="n">
+        <v>24400</v>
+      </c>
+      <c r="L69" t="n">
+        <v>29600</v>
+      </c>
+      <c r="M69" t="n">
+        <v>35500</v>
+      </c>
+      <c r="N69" t="n">
+        <v>25333.33333333333</v>
+      </c>
+      <c r="O69" t="n">
+        <v>29266.66666666667</v>
+      </c>
+      <c r="P69" t="n">
+        <v>341</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>410</v>
+      </c>
+      <c r="R69" t="n">
+        <v>354.3333333333333</v>
+      </c>
+      <c r="S69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="70">
@@ -2185,7 +4794,7 @@
         <v>9</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>45901</v>
+        <v>45930</v>
       </c>
       <c r="E70" t="n">
         <v>30000</v>
@@ -2194,7 +4803,46 @@
         <v>429</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>45901</v>
+        <v>45930</v>
+      </c>
+      <c r="H70" t="n">
+        <v>3</v>
+      </c>
+      <c r="I70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J70" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="K70" t="n">
+        <v>24050</v>
+      </c>
+      <c r="L70" t="n">
+        <v>22000</v>
+      </c>
+      <c r="M70" t="n">
+        <v>28250</v>
+      </c>
+      <c r="N70" t="n">
+        <v>23483.33333333333</v>
+      </c>
+      <c r="O70" t="n">
+        <v>27358.33333333333</v>
+      </c>
+      <c r="P70" t="n">
+        <v>340</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>312</v>
+      </c>
+      <c r="R70" t="n">
+        <v>331</v>
+      </c>
+      <c r="S70" t="n">
+        <v>89</v>
+      </c>
+      <c r="T70" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="71">
@@ -2210,7 +4858,7 @@
         <v>10</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>45931</v>
+        <v>45961</v>
       </c>
       <c r="E71" t="n">
         <v>34550</v>
@@ -2219,7 +4867,46 @@
         <v>475</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>45931</v>
+        <v>45961</v>
+      </c>
+      <c r="H71" t="n">
+        <v>4</v>
+      </c>
+      <c r="I71" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K71" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L71" t="n">
+        <v>24400</v>
+      </c>
+      <c r="M71" t="n">
+        <v>35850</v>
+      </c>
+      <c r="N71" t="n">
+        <v>26150</v>
+      </c>
+      <c r="O71" t="n">
+        <v>27650</v>
+      </c>
+      <c r="P71" t="n">
+        <v>429</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>341</v>
+      </c>
+      <c r="R71" t="n">
+        <v>370</v>
+      </c>
+      <c r="S71" t="n">
+        <v>46</v>
+      </c>
+      <c r="T71" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="72">
@@ -2235,7 +4922,7 @@
         <v>11</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>45962</v>
+        <v>45991</v>
       </c>
       <c r="E72" t="n">
         <v>34200</v>
@@ -2244,7 +4931,46 @@
         <v>474</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>45962</v>
+        <v>45991</v>
+      </c>
+      <c r="H72" t="n">
+        <v>4</v>
+      </c>
+      <c r="I72" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K72" t="n">
+        <v>34550</v>
+      </c>
+      <c r="L72" t="n">
+        <v>24050</v>
+      </c>
+      <c r="M72" t="n">
+        <v>29600</v>
+      </c>
+      <c r="N72" t="n">
+        <v>29533.33333333333</v>
+      </c>
+      <c r="O72" t="n">
+        <v>27433.33333333333</v>
+      </c>
+      <c r="P72" t="n">
+        <v>475</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>340</v>
+      </c>
+      <c r="R72" t="n">
+        <v>414.6666666666667</v>
+      </c>
+      <c r="S72" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="73">
@@ -2260,7 +4986,7 @@
         <v>12</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>45992</v>
+        <v>46022</v>
       </c>
       <c r="E73" t="n">
         <v>30300</v>
@@ -2269,7 +4995,46 @@
         <v>419</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>45992</v>
+        <v>46022</v>
+      </c>
+      <c r="H73" t="n">
+        <v>4</v>
+      </c>
+      <c r="I73" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" t="n">
+        <v>34200</v>
+      </c>
+      <c r="L73" t="n">
+        <v>30000</v>
+      </c>
+      <c r="M73" t="n">
+        <v>22000</v>
+      </c>
+      <c r="N73" t="n">
+        <v>32916.66666666666</v>
+      </c>
+      <c r="O73" t="n">
+        <v>28200</v>
+      </c>
+      <c r="P73" t="n">
+        <v>474</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>429</v>
+      </c>
+      <c r="R73" t="n">
+        <v>459.3333333333333</v>
+      </c>
+      <c r="S73" t="n">
+        <v>-55</v>
+      </c>
+      <c r="T73" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="74">
@@ -2285,7 +5050,7 @@
         <v>10</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>45566</v>
+        <v>45596</v>
       </c>
       <c r="E74" t="n">
         <v>5000</v>
@@ -2294,7 +5059,28 @@
         <v>2</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>45566</v>
+        <v>45596</v>
+      </c>
+      <c r="H74" t="n">
+        <v>4</v>
+      </c>
+      <c r="I74" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -2310,7 +5096,7 @@
         <v>1</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>45658</v>
+        <v>45688</v>
       </c>
       <c r="E75" t="n">
         <v>8000</v>
@@ -2319,7 +5105,34 @@
         <v>4</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>45658</v>
+        <v>45688</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K75" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="n">
+        <v>2</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -2335,7 +5148,7 @@
         <v>2</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>45689</v>
+        <v>45716</v>
       </c>
       <c r="E76" t="n">
         <v>4000</v>
@@ -2344,7 +5157,34 @@
         <v>2</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>45689</v>
+        <v>45716</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K76" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="n">
+        <v>-2</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -2360,7 +5200,7 @@
         <v>5</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>45778</v>
+        <v>45808</v>
       </c>
       <c r="E77" t="n">
         <v>4000</v>
@@ -2369,7 +5209,42 @@
         <v>2</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>45778</v>
+        <v>45808</v>
+      </c>
+      <c r="H77" t="n">
+        <v>2</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J77" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K77" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L77" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="n">
+        <v>5666.666666666667</v>
+      </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>2</v>
+      </c>
+      <c r="R77" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="78">
@@ -2385,7 +5260,7 @@
         <v>6</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>45809</v>
+        <v>45838</v>
       </c>
       <c r="E78" t="n">
         <v>2000</v>
@@ -2394,7 +5269,42 @@
         <v>1</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>45809</v>
+        <v>45838</v>
+      </c>
+      <c r="H78" t="n">
+        <v>2</v>
+      </c>
+      <c r="I78" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K78" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L78" t="n">
+        <v>8000</v>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="n">
+        <v>5333.333333333333</v>
+      </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>4</v>
+      </c>
+      <c r="R78" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="S78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="79">
@@ -2410,7 +5320,7 @@
         <v>10</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>45931</v>
+        <v>45961</v>
       </c>
       <c r="E79" t="n">
         <v>2000</v>
@@ -2419,7 +5329,42 @@
         <v>1</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>45931</v>
+        <v>45961</v>
+      </c>
+      <c r="H79" t="n">
+        <v>4</v>
+      </c>
+      <c r="I79" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K79" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L79" t="n">
+        <v>4000</v>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="n">
+        <v>3333.333333333333</v>
+      </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>2</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="80">
@@ -2435,7 +5380,7 @@
         <v>12</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>45992</v>
+        <v>46022</v>
       </c>
       <c r="E80" t="n">
         <v>2000</v>
@@ -2444,7 +5389,46 @@
         <v>1</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>45992</v>
+        <v>46022</v>
+      </c>
+      <c r="H80" t="n">
+        <v>4</v>
+      </c>
+      <c r="I80" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J80" t="n">
+        <v>1</v>
+      </c>
+      <c r="K80" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L80" t="n">
+        <v>4000</v>
+      </c>
+      <c r="M80" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N80" t="n">
+        <v>2666.666666666667</v>
+      </c>
+      <c r="O80" t="n">
+        <v>4166.666666666667</v>
+      </c>
+      <c r="P80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>2</v>
+      </c>
+      <c r="R80" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
